--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -19757,6 +19757,154 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19790,7 +19938,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -19873,7 +20021,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -19883,7 +20031,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1596,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -3481,9 +3469,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3877,9 +3862,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4025,9 +4007,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4173,9 +4152,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -6049,9 +6025,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6445,9 +6418,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6593,9 +6563,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6741,9 +6708,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -8321,9 +8285,6 @@
       <c r="O49" t="n">
         <v>1780</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.8334790107146373</v>
       </c>
@@ -8617,9 +8578,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9013,9 +8971,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9161,9 +9116,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -9309,9 +9261,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -10889,9 +10838,6 @@
       <c r="O65" t="n">
         <v>1829</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.8564230958410515</v>
       </c>
@@ -11185,9 +11131,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11581,9 +11524,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11729,9 +11669,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11877,9 +11814,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13753,9 +13687,6 @@
       <c r="O83" t="n">
         <v>1459</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.6831718408048627</v>
       </c>
@@ -14049,9 +13980,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14445,9 +14373,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14593,9 +14518,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14741,9 +14663,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -15137,9 +15056,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -15285,9 +15201,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -15433,9 +15346,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15581,9 +15491,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15729,9 +15636,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15877,9 +15781,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16025,9 +15926,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16173,9 +16071,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -16321,9 +16216,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -16469,9 +16361,6 @@
       <c r="O100" t="n">
         <v>461</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.2158616988423864</v>
       </c>
@@ -16617,9 +16506,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17013,9 +16899,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -17161,9 +17044,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -17557,9 +17437,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17705,9 +17582,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17853,9 +17727,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -18001,9 +17872,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -18149,9 +18017,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -18297,9 +18162,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18445,9 +18307,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -18593,9 +18452,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -18741,9 +18597,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18889,9 +18742,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -19285,9 +19135,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19433,9 +19280,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -19827,9 +19671,6 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -19746,6 +19746,151 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19779,7 +19924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -19862,7 +20007,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -19872,7 +20017,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -16462,12 +16462,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16501,95 +16501,84 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O101" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>0.0003538785578469373</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16605,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -16665,98 +16654,23 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -16850,17 +16764,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16894,81 +16808,170 @@
         </is>
       </c>
       <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
         <v>1</v>
       </c>
-      <c r="O103" t="n">
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
         <v>1</v>
       </c>
-      <c r="R103" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
-      <c r="AT103" t="n">
-        <v>0</v>
-      </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17000,12 +17003,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -17039,95 +17042,81 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17143,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17203,98 +17192,23 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -17388,17 +17302,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17423,7 +17337,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -17437,76 +17351,165 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17538,12 +17541,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -17616,42 +17619,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17683,12 +17686,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -17713,7 +17716,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -17761,42 +17764,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17828,12 +17831,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -17906,42 +17909,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17973,12 +17976,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18003,7 +18006,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -18051,42 +18054,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18118,12 +18121,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18196,42 +18199,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18263,12 +18266,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -18293,7 +18296,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18341,42 +18344,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18408,12 +18411,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -18486,42 +18489,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18553,12 +18556,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -18583,7 +18586,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -18631,42 +18634,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18698,12 +18701,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -18728,12 +18731,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -18750,82 +18753,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18841,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -18901,98 +18890,23 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -19086,17 +19000,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19135,76 +19049,165 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19236,12 +19239,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19288,82 +19291,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19379,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -19439,98 +19428,23 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -19624,17 +19538,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19659,7 +19573,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -19673,76 +19587,165 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19807,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -19886,6 +19889,151 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20007,7 +20155,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -20017,7 +20165,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -20069,7 +20217,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7436</v>
+        <v>7441</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -13682,13 +13682,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1459</v>
+        <v>1542</v>
       </c>
       <c r="O83" t="n">
-        <v>1459</v>
+        <v>1542</v>
       </c>
       <c r="R83" t="n">
-        <v>0.6831718408048627</v>
+        <v>0.722036311529197</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -16356,13 +16356,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>461</v>
+        <v>989</v>
       </c>
       <c r="O100" t="n">
-        <v>461</v>
+        <v>989</v>
       </c>
       <c r="R100" t="n">
-        <v>0.2158616988423864</v>
+        <v>0.4630959222453799</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -18846,12 +18846,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -18885,95 +18885,81 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>0.009833179339891788</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -19000,7 +18986,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -19049,98 +19035,23 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -19234,17 +19145,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19283,76 +19194,165 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19384,12 +19384,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19436,82 +19436,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19538,7 +19524,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -19587,98 +19573,23 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -19772,17 +19683,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -19807,7 +19718,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -19821,76 +19732,165 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -20034,6 +20034,151 @@
         </is>
       </c>
       <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20155,7 +20300,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -20165,7 +20310,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -20217,7 +20362,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7441</v>
+        <v>8073</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -13682,13 +13682,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1542</v>
+        <v>1593</v>
       </c>
       <c r="O83" t="n">
-        <v>1542</v>
+        <v>1593</v>
       </c>
       <c r="R83" t="n">
-        <v>0.722036311529197</v>
+        <v>0.7459168899260771</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -16356,13 +16356,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>989</v>
+        <v>1169</v>
       </c>
       <c r="O100" t="n">
-        <v>989</v>
+        <v>1169</v>
       </c>
       <c r="R100" t="n">
-        <v>0.4630959222453799</v>
+        <v>0.5473803165873095</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -18885,13 +18885,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="O116" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="R116" t="n">
-        <v>0.009833179339891788</v>
+        <v>0.04495167698236246</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20179,6 +20179,151 @@
         </is>
       </c>
       <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20217,7 +20362,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20445,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -20310,7 +20455,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -20362,7 +20507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8073</v>
+        <v>8380</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -27247,12 +27247,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27286,13 +27286,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27325,42 +27325,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27392,12 +27392,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27431,95 +27431,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27546,7 +27532,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -27595,98 +27581,23 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -27780,17 +27691,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27815,7 +27726,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27829,76 +27740,165 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27930,12 +27930,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -28008,42 +28008,42 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28075,12 +28075,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -28119,9 +28119,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -28130,77 +28127,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28215,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -28279,98 +28267,18 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -28464,17 +28372,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28499,7 +28407,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -28513,76 +28421,168 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28614,12 +28614,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28692,42 +28692,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28759,12 +28759,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28803,9 +28803,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -28814,77 +28811,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28911,7 +28899,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -28963,98 +28951,18 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -29148,17 +29056,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29183,7 +29091,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -29197,76 +29105,168 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29298,12 +29298,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -29376,42 +29376,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29443,12 +29443,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -29473,7 +29473,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -29487,9 +29487,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -29498,77 +29495,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29595,7 +29583,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -29647,98 +29635,18 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -29832,17 +29740,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29867,7 +29775,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29881,76 +29789,168 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29982,12 +29982,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -30060,42 +30060,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30127,12 +30127,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -30157,7 +30157,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -30205,42 +30205,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30272,12 +30272,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -30316,9 +30316,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -30327,77 +30324,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30412,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -30476,98 +30464,18 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -30661,17 +30569,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30696,90 +30604,182 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>96</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0.04495167698236246</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30811,12 +30811,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30850,95 +30850,81 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>0.04495167698236246</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -30965,7 +30951,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -31014,98 +31000,23 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -31199,17 +31110,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -31243,81 +31154,170 @@
         </is>
       </c>
       <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
         <v>1</v>
       </c>
-      <c r="O179" t="n">
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
         <v>1</v>
       </c>
-      <c r="R179" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
-      <c r="AT179" t="n">
-        <v>0</v>
-      </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31349,12 +31349,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31388,95 +31388,81 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31503,7 +31489,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -31552,98 +31538,23 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -31737,17 +31648,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -31772,7 +31683,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -31786,76 +31697,165 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31887,12 +31887,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -31931,9 +31931,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -31942,77 +31939,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32039,7 +32027,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -32091,98 +32079,18 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
@@ -32276,17 +32184,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32311,7 +32219,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -32325,76 +32233,168 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="R185" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32426,12 +32426,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32470,9 +32470,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -32481,77 +32478,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32578,7 +32566,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -32630,98 +32618,18 @@
       <c r="P187" t="n">
         <v>0</v>
       </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
@@ -32815,17 +32723,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -32850,7 +32758,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -32864,76 +32772,168 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32965,12 +32965,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33009,9 +33009,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33020,77 +33017,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33117,7 +33105,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -33169,98 +33157,18 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -33326,6 +33234,243 @@
         </is>
       </c>
       <c r="BC190" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -33447,7 +33592,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -33457,7 +33602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -946,17 +946,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1172,7 +1177,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1180,17 +1185,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1621,7 +1631,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1629,17 +1639,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1855,7 +1870,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1863,17 +1878,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -5070,7 +5090,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5078,17 +5098,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5304,7 +5329,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5312,17 +5337,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5753,7 +5783,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -5761,17 +5791,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5987,7 +6022,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -5995,17 +6030,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9202,7 +9242,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9210,17 +9250,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -9436,7 +9481,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -9444,17 +9489,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -9885,7 +9935,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -9893,17 +9943,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -10119,7 +10174,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -10127,17 +10182,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -13725,7 +13785,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -13733,17 +13793,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -13959,7 +14024,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -13967,17 +14032,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -14408,7 +14478,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14416,17 +14486,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -14642,7 +14717,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -14650,17 +14725,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -17854,7 +17934,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -17862,17 +17942,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -18088,7 +18173,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -18096,17 +18181,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -18537,7 +18627,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -18545,17 +18635,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -18771,7 +18866,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -18779,17 +18874,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -22673,7 +22773,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -22681,17 +22781,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -22907,7 +23012,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -22915,17 +23020,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -23356,7 +23466,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23364,17 +23474,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -23590,7 +23705,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -23598,17 +23713,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -26923,7 +27043,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -26931,17 +27051,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -27157,7 +27282,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -27165,17 +27290,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -27606,7 +27736,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -27614,17 +27744,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -27840,7 +27975,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -27848,17 +27983,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS159" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -31025,7 +31165,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -31033,17 +31173,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS178" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -31259,7 +31404,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -31267,17 +31412,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -31563,7 +31713,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -31571,17 +31721,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -31797,7 +31952,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -31805,17 +31960,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS182" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1169</v>
+        <v>1258</v>
       </c>
       <c r="O152" t="n">
-        <v>1169</v>
+        <v>1258</v>
       </c>
       <c r="R152" t="n">
-        <v>0.5473803165873095</v>
+        <v>0.5890542671230413</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -30990,13 +30990,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="O177" t="n">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="R177" t="n">
-        <v>0.04495167698236246</v>
+        <v>0.1142521789968379</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -33633,6 +33633,1496 @@
       <c r="BC191" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1</v>
+      </c>
+      <c r="P194" t="n">
+        <v>1</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33669,7 +35159,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -33752,7 +35242,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -33762,7 +35252,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -33782,7 +35272,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -33814,7 +35304,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8387</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="16">
